--- a/Result/profitability/2375.xlsx
+++ b/Result/profitability/2375.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7725</v>
+        <v>0.78625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.48375</v>
+        <v>16.39375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.84375</v>
+        <v>0.8412500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>13.57</v>
+        <v>13.7625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6387499999999999</v>
+        <v>0.61875</v>
       </c>
       <c r="N4" t="n">
-        <v>10.70375</v>
+        <v>10.6125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3075</v>
+        <v>0.41625</v>
       </c>
       <c r="N5" t="n">
-        <v>4.19625</v>
+        <v>3.994999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23125</v>
+        <v>0.195</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1575</v>
+        <v>-0.2800000000000005</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.10125</v>
+        <v>-0.08874999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.68</v>
+        <v>-3.7175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.27375</v>
+        <v>-0.23875</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.27125</v>
+        <v>-7.005000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>-1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6137499999999999</v>
+        <v>-0.61375</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.444999999999999</v>
+        <v>-9.445</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.02</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.67875</v>
+        <v>-0.6787499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>-5.8725</v>
@@ -2026,10 +2026,10 @@
         <v>-0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.55</v>
+        <v>-0.5499999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.647499999999999</v>
+        <v>-1.6475</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1569</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1269</v>
+      </c>
+      <c r="E75" t="n">
+        <v>300</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>137</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49</v>
+      </c>
+      <c r="J75" t="n">
+        <v>186</v>
+      </c>
+      <c r="K75" t="n">
+        <v>115</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.94875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.17375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.358974358974359</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.129999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1255896226415094</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.578947368421053</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07777777777777772</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
